--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -727,7 +727,7 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L8" t="str">
-        <v>Famille ou ami</v>
+        <v>Famille</v>
       </c>
       <c r="M8" t="str">
         <v>Non</v>
@@ -1512,16 +1512,57 @@
         <v>Non</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>CLI-127</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Les délices de Saint Fargeau</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>Les délices de Saint Fargeau</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Prospect</v>
+      </c>
+      <c r="G28" t="str">
+        <v>03 86 74 02 54</v>
+      </c>
+      <c r="H28" t="str">
+        <v>direction-les delices@outlook.fr</v>
+      </c>
+      <c r="I28" t="str">
+        <v>4 Pl. Mal de Lattre de Tassigny</v>
+      </c>
+      <c r="J28" t="str">
+        <v>89170</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Saint-Fargeau</v>
+      </c>
+      <c r="L28" t="str">
+        <v>client qui m'a contacté par téléphone pour une demande de devis et il m'a connu grâce à Delphine, la secrétaire de la mairie de Tannerre.</v>
+      </c>
+      <c r="M28" t="str">
+        <v>Non</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2424,16 +2465,94 @@
         <v>Non</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>CHA-232</v>
+      </c>
+      <c r="B32" t="str">
+        <v>CLI-127</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Vitrines magasin</v>
+      </c>
+      <c r="E32">
+        <v>40</v>
+      </c>
+      <c r="F32" t="str">
+        <v>1h00</v>
+      </c>
+      <c r="G32" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Le client demande une intervention tous les 30 à 45 jours.</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>CHA-233</v>
+      </c>
+      <c r="B33" t="str">
+        <v>TETRE</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Vitres RCH</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33" t="str">
+        <v>1h00</v>
+      </c>
+      <c r="G33" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>CHA-234</v>
+      </c>
+      <c r="B34" t="str">
+        <v>TETRE</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Fenêtre 1ér étage</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34" t="str">
+        <v>30mn</v>
+      </c>
+      <c r="G34" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Non</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2747,9 +2866,35 @@
         <v>Non</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>DEV-312</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CLI-127</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CHA-232</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="E13">
+        <v>40</v>
+      </c>
+      <c r="F13" t="str">
+        <v>En cours</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Nettoyage de la vitrine, de la porte vitrée et du retour vitré coté porte sur les 2 faces. Vitrine dégagé par le client avant mon passage.</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Non</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3256,13 +3401,13 @@
         <v>TETRE</v>
       </c>
       <c r="C15" t="str">
-        <v>CHANT015</v>
+        <v>CHA-233</v>
       </c>
       <c r="D15" t="str">
         <v>2026-09-11</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>18:00</v>
       </c>
       <c r="F15" t="str">
         <v>1,25</v>
@@ -3621,7 +3766,7 @@
         <v>60</v>
       </c>
       <c r="H25" t="str">
-        <v>Planifiée</v>
+        <v>Payée</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -3641,13 +3786,13 @@
         <v>TETRE</v>
       </c>
       <c r="C26" t="str">
-        <v>CHANT015</v>
+        <v>CHA-234</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-18</v>
       </c>
       <c r="E26" t="str">
-        <v>09:00</v>
+        <v>11:00</v>
       </c>
       <c r="F26" t="str">
         <v>1,25</v>
@@ -3656,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="str">
-        <v>Annulée</v>
+        <v>Planifiée</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -4079,7 +4224,7 @@
         <v>AlainB Pro Local</v>
       </c>
       <c r="B2" t="str">
-        <v>V1.6.20</v>
+        <v>V1.6.23</v>
       </c>
       <c r="C2" t="str">
         <v>2026-09-17</v>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:N29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,9 +440,12 @@
         <v>Ville</v>
       </c>
       <c r="L1" t="str">
+        <v>Canal_Obtention</v>
+      </c>
+      <c r="M1" t="str">
         <v>Notes</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Archive</v>
       </c>
     </row>
@@ -481,9 +484,12 @@
         <v>Pourrain</v>
       </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>Client qui m'a contacté par le formulaire du site le 24 mars 2026.Pour un nettoyage véranda et Velux.</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -522,9 +528,12 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>Maison avec 1 étage</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -566,6 +575,9 @@
         <v/>
       </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -604,9 +616,12 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>Grande longère avec double baies vitrées à l'entrée + un coté accéssible avec échelle en bois sur place + nombreuses fenêtres de plein pied + porte fenêtre salon</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -645,9 +660,12 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>Première intervention, vendredi 20 mars 2026</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -686,9 +704,12 @@
         <v>Tannerre en Puisaye</v>
       </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>elle est juste intéressé pour le nettoyage de deux Velux très encrassés</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -727,9 +748,12 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>Famille</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -768,9 +792,12 @@
         <v>Tannnerre en Puisaye</v>
       </c>
       <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>Maison de plein pied - Façade en bois et châssis alu</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -812,6 +839,9 @@
         <v/>
       </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -850,9 +880,12 @@
         <v>Villiers Saint Benoît</v>
       </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>Prestation informatique</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -891,9 +924,12 @@
         <v>Charny-Oréee-de-Puisaye</v>
       </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>Demande pour intervention pour la salle de réception uniquement (domaine composé de plusieurs bâtiments) idéalement à faire entre le 21 et le 24 septembre 2026.</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -932,9 +968,12 @@
         <v>St Privé</v>
       </c>
       <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>M"a contacté par SMS le 2/06/2026 suite post sur FB et lien de mon site</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -973,9 +1012,12 @@
         <v>L’Ouesme</v>
       </c>
       <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>cliente apportée par Céline - Maison bien entretenue à la sortie de Louesme</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1014,9 +1056,12 @@
         <v>Champignelles</v>
       </c>
       <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>à voir avec Nathalie s'il s'agit d'une prestation régulière ou à la demande.</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1055,9 +1100,12 @@
         <v>Tannerre-en-Puisaye</v>
       </c>
       <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>N° Bruno 03 86 45 43 59 (domicile) l'autre N° est celui de sa femme</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1096,9 +1144,12 @@
         <v>TOUCY</v>
       </c>
       <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>Reçu photo verrière par sms le 17/07/2026</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1140,6 +1191,9 @@
         <v/>
       </c>
       <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1181,6 +1235,9 @@
         <v/>
       </c>
       <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1219,9 +1276,12 @@
         <v>Louesme</v>
       </c>
       <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>Privilégiez les messages par WhatsApp, car problème avec son PC.</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1260,9 +1320,12 @@
         <v>Champignelles</v>
       </c>
       <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>Voici les coordonnées de Monsieur (Jean-Claude) : 06 07 59 09 64. Client traité une première fois en 2024 grâce à Anita, mais avec une erreur de tarification, puisque je leur avais proposé que 50 € lors de la première intervention, et j’ai mis plus de 2 heures et demie pour nettoyer toutes les vitres.</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1304,6 +1367,9 @@
         <v/>
       </c>
       <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1345,6 +1411,9 @@
         <v/>
       </c>
       <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1386,6 +1455,9 @@
         <v/>
       </c>
       <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1424,9 +1496,12 @@
         <v>Saint Julien du Sault</v>
       </c>
       <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v>Cliente obtenue grâce à mon site, via le formulaire de contact. Mais hélas, située à 40 minutes de chez moi. Demande pour le nettoyage d'une véranda et des vitres de son pavillon.</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1468,6 +1543,9 @@
         <v/>
       </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1509,6 +1587,9 @@
         <v/>
       </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -1547,22 +1628,69 @@
         <v>Saint-Fargeau</v>
       </c>
       <c r="L28" t="str">
-        <v>client qui m'a contacté par téléphone pour une demande de devis et il m'a connu grâce à Delphine, la secrétaire de la mairie de Tannerre.</v>
+        <v>Recommandation / bouche-à-oreille</v>
       </c>
       <c r="M28" t="str">
+        <v>client qui m'a contacté par téléphone pour une demande de devis et il m'a connu grâce à Delphine, la secrétaire de la mairie de Tannerre. Proposition envoyée par mail le 17 septembre, mais le 22 septembre, aucune réponse de leur part. Je pense qu'ils n'ont pas accepté le devis.</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>CLI-128</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Yaël Maire</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Yaël</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Maire</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>Actif</v>
+      </c>
+      <c r="G29" t="str">
+        <v>06 63 13 15 78</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>11 rue Saint-Blaise</v>
+      </c>
+      <c r="J29" t="str">
+        <v>89350</v>
+      </c>
+      <c r="K29" t="str">
+        <v>Tannerre-en-Puisaye</v>
+      </c>
+      <c r="L29" t="str">
+        <v>Passage ou voisinage</v>
+      </c>
+      <c r="M29" t="str">
+        <v>A faire exclusivement le vendredi pour que la cliente puisse détacher, laver et remettre ses rideaux au fur et à mesure.</v>
+      </c>
+      <c r="N29" t="str">
         <v>Non</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1653,22 +1781,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>CHANT010</v>
+        <v>CHANT020</v>
       </c>
       <c r="B4" t="str">
-        <v>ALPHA</v>
+        <v>CLAUD</v>
       </c>
       <c r="C4" t="str">
         <v>PAVILLON</v>
       </c>
       <c r="D4" t="str">
-        <v>chantier non vu</v>
+        <v>pavillon Avec cinq fenêtres au rez-de-chaussée et une fenêtre au premier étage</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F4" t="str">
-        <v>1h00</v>
+        <v>1,5</v>
       </c>
       <c r="G4" t="str">
         <v>À planifier</v>
@@ -1682,22 +1810,22 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>CHANT018</v>
+        <v>CHA-222</v>
       </c>
       <c r="B5" t="str">
-        <v>MOUY</v>
+        <v>CLAUD</v>
       </c>
       <c r="C5" t="str">
-        <v>PAVILLON</v>
+        <v>Vitres RCH</v>
       </c>
       <c r="D5" t="str">
-        <v>Nettoyage pavillon avec un seul niveau, plus verrière, accolé à la maison, sur l’arrière. Photos complètes envoyée par SMS.</v>
+        <v>Nettoyages vitres plein pieds ouvrant à la française du RCH</v>
       </c>
       <c r="E5">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="F5" t="str">
-        <v>4</v>
+        <v>1h00</v>
       </c>
       <c r="G5" t="str">
         <v>À planifier</v>
@@ -1709,142 +1837,142 @@
         <v>Non</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>CHA-226</v>
+        <v>CHA-227</v>
       </c>
       <c r="B6" t="str">
-        <v>CLI-123</v>
+        <v>CLI-124</v>
       </c>
       <c r="C6" t="str">
-        <v>Vitres Salle des Fêtes</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Vitrage simple à petit bois, grande hauteur.</v>
-      </c>
-      <c r="E6">
-        <v>120</v>
-      </c>
-      <c r="F6" t="str">
-        <v>3</v>
-      </c>
-      <c r="G6" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>CHANT020</v>
-      </c>
-      <c r="B7" t="str">
-        <v>CLAUD</v>
-      </c>
-      <c r="C7" t="str">
-        <v>PAVILLON</v>
-      </c>
-      <c r="D7" t="str">
-        <v>pavillon Avec cinq fenêtres au rez-de-chaussée et une fenêtre au premier étage</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
-      <c r="F7" t="str">
-        <v>1,5</v>
-      </c>
-      <c r="G7" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>CHA-222</v>
-      </c>
-      <c r="B8" t="str">
-        <v>CLAUD</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Vitres RCH</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Nettoyages vitres plein pieds ouvrant à la française du RCH</v>
-      </c>
-      <c r="E8">
-        <v>30</v>
-      </c>
-      <c r="F8" t="str">
-        <v>1h00</v>
-      </c>
-      <c r="G8" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CHA-223</v>
-      </c>
-      <c r="B9" t="str">
-        <v>CLI-123</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Bâtiment administratif</v>
-      </c>
-      <c r="D9" t="str">
-        <v>A voir une fois la visite effectuée.</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="str">
-        <v>0</v>
-      </c>
-      <c r="G9" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
-      <c r="A10" t="str">
-        <v>CHA-227</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CLI-124</v>
-      </c>
-      <c r="C10" t="str">
         <v>Salle de réception</v>
       </c>
-      <c r="D10" t="str" xml:space="preserve">
+      <c r="D6" t="str" xml:space="preserve">
         <v xml:space="preserve">Nettoyage vitres salle de réception, 7 grands panneaux avec impostes et vitrage simple et encadrements bois.
  4 portes fenêtres 2 vanteaux
  1 porte vitrée</v>
       </c>
+      <c r="E6">
+        <v>150</v>
+      </c>
+      <c r="F6" t="str">
+        <v>3h</v>
+      </c>
+      <c r="G6" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Première intervention le mercredi 23 septembre pour une durée réelle de 3 heures. j'ai juste eu besoin de mon échelle debout et surtout du grattoir Triumph</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CHANT011</v>
+      </c>
+      <c r="B7" t="str">
+        <v>YTHIE</v>
+      </c>
+      <c r="C7" t="str">
+        <v>PAVILLON</v>
+      </c>
+      <c r="D7" t="str">
+        <v>RCH - 5 fenêtres double vitrage classique de plein pied</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7" t="str">
+        <v>0,75</v>
+      </c>
+      <c r="G7" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CHANT015</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TETRE</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Maison Tetrel RCH+1er</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Nettoyage des vitres et portes-fenêtres rez-de-chaussée + 1er étage.</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1,25</v>
+      </c>
+      <c r="G8" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CHANT019</v>
+      </c>
+      <c r="B9" t="str">
+        <v>GUILL</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Maison Guillemin-Vilaine</v>
+      </c>
+      <c r="D9" t="str">
+        <v>vitres châssis PVC avec fenêtre, ouvrante à la française accessible par l’extérieur au rez-de-chaussée, plus baie vitrée dans le séjour, deux fenêtres, chiens, assis au premier étage et un VELUX au premier étage.</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2,5</v>
+      </c>
+      <c r="G9" t="str">
+        <v>À planifier</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CHANT009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>JOLYBE</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Maison Joly-Bernard</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Grande baie vitrée avec imposte côté jardin- Trois petites fenêtres ouvrant à la française côté rue</v>
+      </c>
       <c r="E10">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F10" t="str">
-        <v>5 h</v>
+        <v>2</v>
       </c>
       <c r="G10" t="str">
         <v>À planifier</v>
@@ -1858,22 +1986,22 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CHANT011</v>
+        <v>CHANT001</v>
       </c>
       <c r="B11" t="str">
-        <v>YTHIE</v>
+        <v>RIFFAU</v>
       </c>
       <c r="C11" t="str">
-        <v>PAVILLON</v>
+        <v>PAVILLON Riffault</v>
       </c>
       <c r="D11" t="str">
-        <v>RCH - 5 fenêtres double vitrage classique de plein pied</v>
+        <v>Pavillon vitres au rez-de-chaussée et au premier étage.</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F11" t="str">
-        <v>0,75</v>
+        <v>1</v>
       </c>
       <c r="G11" t="str">
         <v>À planifier</v>
@@ -1887,22 +2015,22 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CHANT015</v>
+        <v>CHANT005</v>
       </c>
       <c r="B12" t="str">
-        <v>TETRE</v>
+        <v>MAIRI</v>
       </c>
       <c r="C12" t="str">
-        <v>PAVILLON</v>
+        <v>Petite salle des fêtes</v>
       </c>
       <c r="D12" t="str">
-        <v>Nettoyage des vitres et portes-fenêtres rez-de-chaussée + 1er étage.</v>
+        <v>Vitres à petits carreaux</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F12" t="str">
-        <v>1,25</v>
+        <v>2,5</v>
       </c>
       <c r="G12" t="str">
         <v>À planifier</v>
@@ -1916,19 +2044,19 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CHANT019</v>
+        <v>CHANT017</v>
       </c>
       <c r="B13" t="str">
-        <v>GUILL</v>
+        <v>FICHE</v>
       </c>
       <c r="C13" t="str">
-        <v>Maison Guillemin-Vilaine</v>
+        <v>PAVILLON</v>
       </c>
       <c r="D13" t="str">
-        <v>vitres châssis PVC avec fenêtre, ouvrante à la française accessible par l’extérieur au rez-de-chaussée, plus baie vitrée dans le séjour, deux fenêtres, chiens, assis au premier étage et un VELUX au premier étage.</v>
+        <v>Gros pavillon sur 3 niveaux, avec SAS au rez-de-chaussée, plus 3 fenêtres dans le garage et la buanderie. Au premier étage, de grandes portes-fenêtres triples, plus trois fenêtres triples, et une petite dans la cuisine. Au premier étage : deux Velux (dont un petit dans les toilettes), une petite fenêtre tout juste accessible au-dessus de l’escalier, et dans les chambres deux triple fenêtres et deux autres fenêtres sur la façade côté piscine.</v>
       </c>
       <c r="E13">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F13" t="str">
         <v>2,5</v>
@@ -1945,22 +2073,22 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CHANT009</v>
+        <v>CHANT013</v>
       </c>
       <c r="B14" t="str">
-        <v>JOLYBE</v>
+        <v>LOUAU</v>
       </c>
       <c r="C14" t="str">
-        <v>Maison Joly-Bernard</v>
+        <v>PAVILLON</v>
       </c>
       <c r="D14" t="str">
-        <v>Grande baie vitrée avec imposte côté jardin- Trois petites fenêtres ouvrant à la française côté rue</v>
+        <v>chantier non vu</v>
       </c>
       <c r="E14">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F14" t="str">
-        <v>2</v>
+        <v>1h00</v>
       </c>
       <c r="G14" t="str">
         <v>À planifier</v>
@@ -1974,19 +2102,19 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CHANT001</v>
+        <v>CHANT007</v>
       </c>
       <c r="B15" t="str">
-        <v>RIFFAU</v>
+        <v>MAIRI</v>
       </c>
       <c r="C15" t="str">
-        <v>PAVILLON Riffault</v>
+        <v>Salle de sport AST</v>
       </c>
       <c r="D15" t="str">
-        <v>Pavillon vitres au rez-de-chaussée et au premier étage.</v>
+        <v>Double vitrage - Fenêtre ouvrant à la française</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F15" t="str">
         <v>1</v>
@@ -2003,22 +2131,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CHANT005</v>
+        <v>CHANT003</v>
       </c>
       <c r="B16" t="str">
-        <v>MAIRI</v>
+        <v>BARB02</v>
       </c>
       <c r="C16" t="str">
-        <v>Petite salle des fêtes</v>
+        <v>Maison Bruno et Valérie</v>
       </c>
       <c r="D16" t="str">
-        <v>Vitres à petits carreaux</v>
+        <v>Vélux large grande hauteur séjour + fenêtre séjour + marquise verre cathédrale</v>
       </c>
       <c r="E16">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F16" t="str">
-        <v>2,5</v>
+        <v>2</v>
       </c>
       <c r="G16" t="str">
         <v>À planifier</v>
@@ -2032,22 +2160,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CHANT017</v>
+        <v>CHA-225</v>
       </c>
       <c r="B17" t="str">
-        <v>FICHE</v>
+        <v>CLI-123</v>
       </c>
       <c r="C17" t="str">
-        <v>PAVILLON</v>
+        <v>Vitres Mairie</v>
       </c>
       <c r="D17" t="str">
-        <v>Gros pavillon sur 3 niveaux, avec SAS au rez-de-chaussée, plus 3 fenêtres dans le garage et la buanderie. Au premier étage, de grandes portes-fenêtres triples, plus trois fenêtres triples, et une petite dans la cuisine. Au premier étage : deux Velux (dont un petit dans les toilettes), une petite fenêtre tout juste accessible au-dessus de l’escalier, et dans les chambres deux triple fenêtres et deux autres fenêtres sur la façade côté piscine.</v>
+        <v/>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F17" t="str">
-        <v>2,5</v>
+        <v>2h30</v>
       </c>
       <c r="G17" t="str">
         <v>À planifier</v>
@@ -2061,22 +2189,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CHANT013</v>
+        <v>CHA-221</v>
       </c>
       <c r="B18" t="str">
-        <v>LOUAU</v>
+        <v>CLI-121</v>
       </c>
       <c r="C18" t="str">
-        <v>PAVILLON</v>
+        <v>Vitres maison</v>
       </c>
       <c r="D18" t="str">
-        <v>chantier non vu</v>
+        <v>Longères avec nombreuses fenêtres de plein pieds + 1 porte fenêtre + 1 baie vitrées coulissantes 2 panneaux + retour vitrage fixe et imposte</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" t="str">
-        <v>1h00</v>
+        <v>1h30</v>
       </c>
       <c r="G18" t="str">
         <v>À planifier</v>
@@ -2090,22 +2218,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CHANT007</v>
+        <v>CHA-229</v>
       </c>
       <c r="B19" t="str">
-        <v>MAIRI</v>
+        <v>CLI-125</v>
       </c>
       <c r="C19" t="str">
-        <v>Salle de sport AST</v>
+        <v>Vitres maison dans corps de ferme</v>
       </c>
       <c r="D19" t="str">
-        <v>Double vitrage - Fenêtre ouvrant à la française</v>
+        <v>8 fenêtres avec double vitrages, châssis PVC à hauteur d'homme.</v>
       </c>
       <c r="E19">
         <v>30</v>
       </c>
       <c r="F19" t="str">
-        <v>1</v>
+        <v>1h00</v>
       </c>
       <c r="G19" t="str">
         <v>À planifier</v>
@@ -2119,22 +2247,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CHANT003</v>
+        <v>CHA-231</v>
       </c>
       <c r="B20" t="str">
-        <v>BARB02</v>
+        <v>CLI-126</v>
       </c>
       <c r="C20" t="str">
-        <v>Maison Bruno et Valérie</v>
+        <v>Vitres Annexe</v>
       </c>
       <c r="D20" t="str">
-        <v>Vélux large grande hauteur séjour + fenêtre séjour + marquise verre cathédrale</v>
+        <v>Nettoyage vitres exter + porte vitrées 2 faces</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F20" t="str">
-        <v>2</v>
+        <v>45 mn</v>
       </c>
       <c r="G20" t="str">
         <v>À planifier</v>
@@ -2148,22 +2276,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CHA-225</v>
+        <v>CHA-230</v>
       </c>
       <c r="B21" t="str">
-        <v>CLI-123</v>
+        <v>CLI-126</v>
       </c>
       <c r="C21" t="str">
-        <v>Vitres Mairie</v>
+        <v>Vitres pharmacie complète</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>nettoyage vitres complet Pharmacie (vente, réserve et consultation)</v>
       </c>
       <c r="E21">
         <v>90</v>
       </c>
       <c r="F21" t="str">
-        <v>2h30</v>
+        <v>1h15</v>
       </c>
       <c r="G21" t="str">
         <v>À planifier</v>
@@ -2177,22 +2305,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CHA-221</v>
+        <v>CHA-220</v>
       </c>
       <c r="B22" t="str">
-        <v>CLI-121</v>
+        <v>CLI-119</v>
       </c>
       <c r="C22" t="str">
-        <v>Vitres maison</v>
+        <v>Velux</v>
       </c>
       <c r="D22" t="str">
-        <v>Longères avec nombreuses fenêtres de plein pieds + 1 porte fenêtre + 1 baie vitrées coulissantes 2 panneaux + retour vitrage fixe et imposte</v>
+        <v>2 Velux à nettoyer.</v>
       </c>
       <c r="E22">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F22" t="str">
-        <v>1h30</v>
+        <v>,5</v>
       </c>
       <c r="G22" t="str">
         <v>À planifier</v>
@@ -2206,22 +2334,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CHA-229</v>
+        <v>CHA-228</v>
       </c>
       <c r="B23" t="str">
-        <v>CLI-125</v>
+        <v>ALPHA</v>
       </c>
       <c r="C23" t="str">
-        <v>Vitres maison dans corps de ferme</v>
+        <v>Vitres maison grande hauteur</v>
       </c>
       <c r="D23" t="str">
-        <v>8 fenêtres avec double vitrages, châssis PVC à hauteur d'homme.</v>
+        <v>grandes vitres séjour et chambre + 3 fenêtres cuisine + porte entrée+ miroirs dressing (Utilisation de l'escabeau pour l'intérieur du séjour)</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F23" t="str">
-        <v>1h00</v>
+        <v>2</v>
       </c>
       <c r="G23" t="str">
         <v>À planifier</v>
@@ -2235,22 +2363,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CHA-231</v>
+        <v>CHANT002</v>
       </c>
       <c r="B24" t="str">
-        <v>CLI-126</v>
+        <v>VITTET</v>
       </c>
       <c r="C24" t="str">
-        <v>Vitres Annexe</v>
+        <v>Châlet Bernard &amp; Marie Claire</v>
       </c>
       <c r="D24" t="str">
-        <v>Nettoyage vitres exter + porte vitrées 2 faces</v>
+        <v>Rez de chaussée - Chalet, avec véranda.</v>
       </c>
       <c r="E24">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F24" t="str">
-        <v>45 mn</v>
+        <v>0,75</v>
       </c>
       <c r="G24" t="str">
         <v>À planifier</v>
@@ -2264,22 +2392,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CHA-230</v>
+        <v>CHANT006</v>
       </c>
       <c r="B25" t="str">
-        <v>CLI-126</v>
+        <v>MAIRI</v>
       </c>
       <c r="C25" t="str">
-        <v>Vitres pharmacie complète</v>
+        <v>Grande Salle des fêtes</v>
       </c>
       <c r="D25" t="str">
-        <v>nettoyage vitres complet Pharmacie (vente, réserve et consultation)</v>
+        <v>Vitres chassis métal blanc avec rideaux toile éléctrique</v>
       </c>
       <c r="E25">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F25" t="str">
-        <v>1h15</v>
+        <v>2,5</v>
       </c>
       <c r="G25" t="str">
         <v>À planifier</v>
@@ -2293,22 +2421,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CHA-220</v>
+        <v>CHANT012</v>
       </c>
       <c r="B26" t="str">
-        <v>CLI-119</v>
+        <v>SOURC</v>
       </c>
       <c r="C26" t="str">
-        <v>Velux</v>
+        <v>PAVILLON</v>
       </c>
       <c r="D26" t="str">
-        <v>2 Velux à nettoyer.</v>
+        <v>RCH - 2 portes vitrées - 3 fenêtres - 1ér étage 3 velux + 2 fenêtres</v>
       </c>
       <c r="E26">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F26" t="str">
-        <v>,5</v>
+        <v>1,25</v>
       </c>
       <c r="G26" t="str">
         <v>À planifier</v>
@@ -2322,28 +2450,28 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CHA-224</v>
+        <v>CHA-232</v>
       </c>
       <c r="B27" t="str">
-        <v>CLI-123</v>
+        <v>CLI-127</v>
       </c>
       <c r="C27" t="str">
-        <v>Ecole et cantine</v>
+        <v>Vitrines magasin</v>
       </c>
       <c r="D27" t="str">
-        <v>Ecole - Deux classes avec vitres grande hauteur à petit bois plus vitres accessibles cantine.</v>
+        <v/>
       </c>
       <c r="E27">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="F27" t="str">
-        <v>7</v>
+        <v>1h00</v>
       </c>
       <c r="G27" t="str">
         <v>À planifier</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>Le client demande une intervention tous les 30 à 45 jours.</v>
       </c>
       <c r="I27" t="str">
         <v>Non</v>
@@ -2351,22 +2479,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CHA-228</v>
+        <v>CHA-233</v>
       </c>
       <c r="B28" t="str">
-        <v>ALPHA</v>
+        <v>TETRE</v>
       </c>
       <c r="C28" t="str">
-        <v>Vitres maison grande hauteur</v>
+        <v>Vitres RCH</v>
       </c>
       <c r="D28" t="str">
-        <v>grandes vitres séjour et chambre + 3 fenêtres cuisine + porte entrée+ miroirs dressing (Utilisation de l'escabeau pour l'intérieur du séjour)</v>
+        <v/>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" t="str">
-        <v>2</v>
+        <v>1h00</v>
       </c>
       <c r="G28" t="str">
         <v>À planifier</v>
@@ -2380,22 +2508,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CHANT002</v>
+        <v>CHA-234</v>
       </c>
       <c r="B29" t="str">
-        <v>VITTET</v>
+        <v>TETRE</v>
       </c>
       <c r="C29" t="str">
-        <v>Châlet Bernard &amp; Marie Claire</v>
+        <v>Fenêtre 1ér étage</v>
       </c>
       <c r="D29" t="str">
-        <v>Rez de chaussée - Chalet, avec véranda.</v>
+        <v/>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F29" t="str">
-        <v>0,75</v>
+        <v>30mn</v>
       </c>
       <c r="G29" t="str">
         <v>À planifier</v>
@@ -2407,24 +2535,25 @@
         <v>Non</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
-        <v>CHANT006</v>
+        <v>CHA-235</v>
       </c>
       <c r="B30" t="str">
-        <v>MAIRI</v>
+        <v>CLI-128</v>
       </c>
       <c r="C30" t="str">
-        <v>Grande Salle des fêtes</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Vitres chassis métal blanc avec rideaux toile éléctrique</v>
+        <v>Maison Yël  RCH +1er</v>
+      </c>
+      <c r="D30" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nettoyage vitre complet maison, rez de chaussée plus premier étage
+Comprenant :  Façade rue 5 fenêtres avec petits bois + 1porte  avec une vitre granitée avec imposte - Coté cour 1 fenêtre petits bois - Arrière 4 fenêtres petits bois +1 porte  avec une vitre claire avec imposte.</v>
       </c>
       <c r="E30">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F30" t="str">
-        <v>2,5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="str">
         <v>À planifier</v>
@@ -2436,123 +2565,16 @@
         <v>Non</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>CHANT012</v>
-      </c>
-      <c r="B31" t="str">
-        <v>SOURC</v>
-      </c>
-      <c r="C31" t="str">
-        <v>PAVILLON</v>
-      </c>
-      <c r="D31" t="str">
-        <v>RCH - 2 portes vitrées - 3 fenêtres - 1ér étage 3 velux + 2 fenêtres</v>
-      </c>
-      <c r="E31">
-        <v>40</v>
-      </c>
-      <c r="F31" t="str">
-        <v>1,25</v>
-      </c>
-      <c r="G31" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>CHA-232</v>
-      </c>
-      <c r="B32" t="str">
-        <v>CLI-127</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Vitrines magasin</v>
-      </c>
-      <c r="E32">
-        <v>40</v>
-      </c>
-      <c r="F32" t="str">
-        <v>1h00</v>
-      </c>
-      <c r="G32" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H32" t="str">
-        <v>Le client demande une intervention tous les 30 à 45 jours.</v>
-      </c>
-      <c r="I32" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>CHA-233</v>
-      </c>
-      <c r="B33" t="str">
-        <v>TETRE</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Vitres RCH</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" t="str">
-        <v>1h00</v>
-      </c>
-      <c r="G33" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>CHA-234</v>
-      </c>
-      <c r="B34" t="str">
-        <v>TETRE</v>
-      </c>
-      <c r="C34" t="str">
-        <v>Fenêtre 1ér étage</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" t="str">
-        <v>30mn</v>
-      </c>
-      <c r="G34" t="str">
-        <v>À planifier</v>
-      </c>
-      <c r="H34" t="str">
-        <v/>
-      </c>
-      <c r="I34" t="str">
-        <v>Non</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:K13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2565,18 +2587,27 @@
         <v>ID_Chantier</v>
       </c>
       <c r="D1" t="str">
+        <v>ID_Chantiers</v>
+      </c>
+      <c r="E1" t="str">
         <v>Date_Creation</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Montant</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Statut_Devis</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>Date_Visite</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Heure_Visite</v>
+      </c>
+      <c r="J1" t="str">
         <v>Notes</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>Archive</v>
       </c>
     </row>
@@ -2591,18 +2622,27 @@
         <v>CHANT019</v>
       </c>
       <c r="D2" t="str">
+        <v>CHANT019</v>
+      </c>
+      <c r="E2" t="str">
         <v>2026-05-26</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>60</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2617,18 +2657,27 @@
         <v/>
       </c>
       <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
         <v>2026-03-27</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
       <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2643,18 +2692,27 @@
         <v>CHA-227</v>
       </c>
       <c r="D4" t="str">
+        <v>CHA-227</v>
+      </c>
+      <c r="E4" t="str">
         <v>2026-09-04</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>150</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2669,18 +2727,27 @@
         <v>CHA-221</v>
       </c>
       <c r="D5" t="str">
+        <v>CHA-221</v>
+      </c>
+      <c r="E5" t="str">
         <v>2026-07-17</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>100</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Refusé</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2692,21 +2759,30 @@
         <v>CLI-123</v>
       </c>
       <c r="C6" t="str">
-        <v>CHA-224</v>
+        <v>CHA-226</v>
       </c>
       <c r="D6" t="str">
+        <v>CHA-226 | CHA-225 | CHA-224</v>
+      </c>
+      <c r="E6" t="str">
         <v>2026-08-28</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>590</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>Refusé</v>
       </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2721,18 +2797,27 @@
         <v>CHANT013</v>
       </c>
       <c r="D7" t="str">
+        <v>CHANT013</v>
+      </c>
+      <c r="E7" t="str">
         <v>2026-03-26</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>En cours</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2747,18 +2832,27 @@
         <v>CHANT018</v>
       </c>
       <c r="D8" t="str">
+        <v>CHANT018</v>
+      </c>
+      <c r="E8" t="str">
         <v>2026-05-13</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>200</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>Refusé</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2773,18 +2867,27 @@
         <v>CHANT019</v>
       </c>
       <c r="D9" t="str">
+        <v>CHANT019</v>
+      </c>
+      <c r="E9" t="str">
         <v>2026-04-14</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>60</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2799,18 +2902,27 @@
         <v>CHANT020</v>
       </c>
       <c r="D10" t="str">
+        <v>CHANT020</v>
+      </c>
+      <c r="E10" t="str">
         <v>2026-06-03</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>70</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>En cours</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2825,18 +2937,27 @@
         <v>CHANT009</v>
       </c>
       <c r="D11" t="str">
+        <v>CHANT009</v>
+      </c>
+      <c r="E11" t="str">
         <v>2026-03-25</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>70</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <v>Non</v>
       </c>
     </row>
@@ -2851,22 +2972,31 @@
         <v>CHANT020</v>
       </c>
       <c r="D12" t="str">
+        <v>CHANT020</v>
+      </c>
+      <c r="E12" t="str">
         <v>2026-04-19</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>50</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>Accepté</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
       <c r="H12" t="str">
-        <v>Non</v>
-      </c>
-    </row>
-    <row r="13">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>DEV-312</v>
       </c>
@@ -2877,31 +3007,41 @@
         <v>CHA-232</v>
       </c>
       <c r="D13" t="str">
+        <v>CHA-232</v>
+      </c>
+      <c r="E13" t="str">
         <v>2026-09-17</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>40</v>
       </c>
-      <c r="F13" t="str">
-        <v>En cours</v>
-      </c>
       <c r="G13" t="str">
-        <v>Nettoyage de la vitrine, de la porte vitrée et du retour vitré coté porte sur les 2 faces. Vitrine dégagé par le client avant mon passage.</v>
+        <v>Refusé</v>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">Nettoyage de la vitrine, de la porte vitrée et du retour vitré coté porte sur les 2 faces. Vitrine dégagé par le client avant mon passage.
+Aucune réponse le jeudi 24 septembre, je considère que le client n'a pas accepté ma proposition. Et ça m'arrange car me déplacer pour une si petite vitrine, ce n'était pas rentable pour moi car j'avais 40 minutes de déplacement aller-retour.</v>
+      </c>
+      <c r="K13" t="str">
         <v>Non</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2996,7 +3136,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="str">
-        <v>Terminée</v>
+        <v>Payée</v>
       </c>
       <c r="I3" t="str">
         <v>FAC-2026-002</v>
@@ -3168,16 +3308,16 @@
         <v>2h00</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H8" t="str">
-        <v>Facturée</v>
+        <v>Payée</v>
       </c>
       <c r="I8" t="str">
         <v/>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>Toujours en attente de rglt</v>
       </c>
       <c r="K8" t="str">
         <v>Non</v>
@@ -3203,13 +3343,13 @@
         <v>5h</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H9" t="str">
-        <v>Planifiée</v>
+        <v>Payée</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>FAC-2026-003</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -3346,7 +3486,7 @@
         <v>30</v>
       </c>
       <c r="H13" t="str">
-        <v>Terminée</v>
+        <v>Payée</v>
       </c>
       <c r="I13" t="str">
         <v>FAC-2026-002</v>
@@ -3801,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="str">
-        <v>Planifiée</v>
+        <v>Payée</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -3883,16 +4023,191 @@
         <v>Non</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>INT-429</v>
+      </c>
+      <c r="B29" t="str">
+        <v>MAIRI</v>
+      </c>
+      <c r="C29" t="str">
+        <v>CHANT008</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="E29" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29">
+        <v>150</v>
+      </c>
+      <c r="H29" t="str">
+        <v>Planifiée</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>INT-430</v>
+      </c>
+      <c r="B30" t="str">
+        <v>MAIRI</v>
+      </c>
+      <c r="C30" t="str">
+        <v>CHANT007</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="E30" t="str">
+        <v>11:00</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30">
+        <v>30</v>
+      </c>
+      <c r="H30" t="str">
+        <v>Planifiée</v>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>INT-431</v>
+      </c>
+      <c r="B31" t="str">
+        <v>MAIRI</v>
+      </c>
+      <c r="C31" t="str">
+        <v>CHANT005</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E31" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2h30</v>
+      </c>
+      <c r="G31">
+        <v>150</v>
+      </c>
+      <c r="H31" t="str">
+        <v>Terminée</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>INT-432</v>
+      </c>
+      <c r="B32" t="str">
+        <v>MAIRI</v>
+      </c>
+      <c r="C32" t="str">
+        <v>CHANT006</v>
+      </c>
+      <c r="D32" t="str">
+        <v>2026-09-29</v>
+      </c>
+      <c r="E32" t="str">
+        <v>12:00</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2h30</v>
+      </c>
+      <c r="G32">
+        <v>150</v>
+      </c>
+      <c r="H32" t="str">
+        <v>Terminée</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>INT-433</v>
+      </c>
+      <c r="B33" t="str">
+        <v>CLI-128</v>
+      </c>
+      <c r="C33" t="str">
+        <v>CHA-235</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-10-02</v>
+      </c>
+      <c r="E33" t="str">
+        <v>09:00</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2h</v>
+      </c>
+      <c r="G33">
+        <v>50</v>
+      </c>
+      <c r="H33" t="str">
+        <v>Planifiée</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v>prévoir l'échelle 2 éléments pour faire les vitres du rez-de-chaussée directement par l'extérieur.</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Non</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K33"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3946,19 +4261,19 @@
         <v>480</v>
       </c>
       <c r="F2" t="str">
-        <v>Émise</v>
+        <v>Payée</v>
       </c>
       <c r="G2" t="str">
         <v>Virement</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>2026-06-17</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>Virement par le SGC d'Auxerrre</v>
       </c>
       <c r="K2" t="str">
         <v>Non</v>
@@ -3981,27 +4296,62 @@
         <v>120</v>
       </c>
       <c r="F3" t="str">
-        <v>Émise</v>
+        <v>Payée</v>
       </c>
       <c r="G3" t="str">
         <v>Virement</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>2026-09-15</v>
       </c>
       <c r="I3">
+        <v>120</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>Non</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>FAC-2026-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>CLI-124</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="D4" t="str">
+        <v>INT-419</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Émise</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Virement</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>Non</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4047,7 +4397,7 @@
         <v>SMS</v>
       </c>
       <c r="E2" t="str">
-        <v>Intervention programmée</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>Proposition de nettoyage de vitres (mois en cours)</v>
@@ -4070,7 +4420,7 @@
         <v>Téléphone</v>
       </c>
       <c r="E3" t="str">
-        <v>Intervention programmée</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>Proposition de nettoyage de vitres (mois en cours)</v>
@@ -4093,7 +4443,7 @@
         <v>Téléphone</v>
       </c>
       <c r="E4" t="str">
-        <v>Intervention programmée</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v>Proposition de nettoyage de vitres (mois en cours)</v>
@@ -4116,7 +4466,7 @@
         <v>Email</v>
       </c>
       <c r="E5" t="str">
-        <v>À relancer</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v>Proposition de nettoyage de vitres (mois en cours)</v>
@@ -4224,13 +4574,13 @@
         <v>AlainB Pro Local</v>
       </c>
       <c r="B2" t="str">
-        <v>V1.6.23</v>
+        <v>V1.6.40</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-09-17</v>
+        <v>2026-10-02</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="str">
         <v>AlainB Pro</v>
@@ -4245,13 +4595,13 @@
         <v>Micro-entreprise</v>
       </c>
       <c r="I2" t="str">
-        <v>17, rue de l'Estrade</v>
+        <v>27 rue de l'Estrade</v>
       </c>
       <c r="J2" t="str">
         <v>89350</v>
       </c>
       <c r="K2" t="str">
-        <v>Tannerre-en-Puisaye</v>
+        <v>Tannerre en Puisaye</v>
       </c>
       <c r="L2" t="str">
         <v>06 46 13 35 90</v>
@@ -4260,7 +4610,7 @@
         <v>alainb.vitresnet@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>https://bassalin.wixsite.com/nettoyage-vitres</v>
+        <v>alainb.vitresnet@gmail.com</v>
       </c>
       <c r="O2" t="str">
         <v>33495013600039</v>
@@ -4272,7 +4622,7 @@
         <v>TVA non applicable, art. 293 B du CGI</v>
       </c>
       <c r="R2" t="str">
-        <v>Accepte les règlement en espèces ou par virement uniquement</v>
+        <v>Accepte les règlement en espèces ou par virement uniquement.</v>
       </c>
       <c r="S2" t="str">
         <v>BASSALAIR Alain</v>
@@ -4290,10 +4640,10 @@
         <v>Règlement par virement bancaire</v>
       </c>
       <c r="X2" t="str">
-        <v>FAC</v>
+        <v>FAC2026-</v>
       </c>
       <c r="Y2" t="str">
-        <v>mes/Data/Documents/Appli gestion lavage vitres/Nouvelle Apps sept2026/AlainB-Pro-Icone-iPad.png</v>
+        <v/>
       </c>
       <c r="Z2" t="str">
         <v>Paiement à réception de facture</v>
